--- a/artfynd/A 11490-2022 artfynd.xlsx
+++ b/artfynd/A 11490-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11490-2022 artfynd.xlsx
+++ b/artfynd/A 11490-2022 artfynd.xlsx
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>

--- a/artfynd/A 11490-2022 artfynd.xlsx
+++ b/artfynd/A 11490-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109755935</v>
+        <v>109754481</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599947.3739195887</v>
+        <v>600014</v>
       </c>
       <c r="R2" t="n">
-        <v>7035461.369628038</v>
+        <v>7035374</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109755310</v>
+        <v>109755087</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,40 +794,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600032.6816041055</v>
+        <v>600006</v>
       </c>
       <c r="R3" t="n">
-        <v>7035358.326561471</v>
+        <v>7035303</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,37 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109754481</v>
+        <v>109753866</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600013.3427470266</v>
+        <v>599947</v>
       </c>
       <c r="R4" t="n">
-        <v>7035374.295002658</v>
+        <v>7035350</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,12 +1002,7 @@
         <v>109754588</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600013.5250152375</v>
+        <v>600014</v>
       </c>
       <c r="R5" t="n">
-        <v>7035354.143290731</v>
+        <v>7035354</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109753866</v>
+        <v>109755935</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599946.8127830587</v>
+        <v>599947</v>
       </c>
       <c r="R6" t="n">
-        <v>7035350.263907433</v>
+        <v>7035461</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,32 +1215,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109754255</v>
+        <v>109755310</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1291,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600009.6038129798</v>
+        <v>600032</v>
       </c>
       <c r="R7" t="n">
-        <v>7035379.105312838</v>
+        <v>7035359</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1326,7 +1291,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,14 +1301,14 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1360,6 +1325,232 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>109754255</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hömyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600009</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7035379</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>109753494</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599858</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7035398</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11490-2022 artfynd.xlsx
+++ b/artfynd/A 11490-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109754481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109755087</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109753866</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109754588</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109755935</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109755310</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109754255</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,8 +1591,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109753494</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>